--- a/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/04_Thong_Ke_Thep_Chi_Tiet_BBS_396_Dong.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/04_Thong_Ke_Thep_Chi_Tiet_BBS_396_Dong.xlsx
@@ -4805,7 +4805,7 @@
       </c>
       <c r="R63" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="R65" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="R66" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="R69" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="R70" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="R71" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="R73" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="R74" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="R75" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="R76" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="R77" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="R78" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="R79" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="R80" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="R81" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="R82" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="R83" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="R84" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="R85" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="R86" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="R87" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="R88" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="R89" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="R90" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="R91" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="R92" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="R93" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="R94" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="R95" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="R96" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="R97" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="R98" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="R99" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="R100" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="R101" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="R102" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="R103" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="R104" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="R105" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="R106" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="R107" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="R108" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="R109" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="R110" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="R111" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="R112" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="R113" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="R114" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="R115" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="R116" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="R117" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="R118" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="R119" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40 | BBS vẫn giữ thanh này để gia công (có dài và số lượng trên bản vẽ) nên BBS lớn hơn tổng bản vẽ phần này — chủ dự án quyết định và ghim</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40 | Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="R120" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40 | BBS vẫn giữ thanh này để gia công (có dài và số lượng trên bản vẽ) nên BBS lớn hơn tổng bản vẽ phần này — chủ dự án quyết định và ghim</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40 | Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="R121" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="R122" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40 | BBS vẫn giữ thanh này để gia công (có dài và số lượng trên bản vẽ) nên BBS lớn hơn tổng bản vẽ phần này — chủ dự án quyết định và ghim</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40 | Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="R123" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="R124" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="R125" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg)</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg)</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="R126" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="R127" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="R128" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="R129" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="R130" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.648,73 kg) | OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>Thay theo tr.40 (BBS cũ 19.981,23 kg, bản vẽ 19.885,78 kg) | OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
     </row>
@@ -31956,13 +31956,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>19648.73</v>
+        <v>19885.78</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>19876.96</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>228.23</v>
+        <v>-8.82</v>
       </c>
       <c r="I5" s="10" t="inlineStr"/>
     </row>
@@ -32414,7 +32414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -32570,17 +32570,17 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 19.981,23 kg; bản vẽ 19.648,73 kg</t>
+          <t>Bản vẽ ghi 0 kg cho một số thanh (dài × SL × kg/m = 237,05 kg); Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót) → tổng đối chiếu = tổng bản vẽ + 237,05 kg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.981,23 kg</t>
+          <t>19.648,73 kg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19.648,73 kg</t>
+          <t>19.885,78 kg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -32597,28 +32597,28 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Bệ móng)</t>
+          <t>Mố M2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 18.877,75 kg; bản vẽ 32.355,66 kg</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 19.981,23 kg; bản vẽ 19.885,78 kg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.877,75 kg</t>
+          <t>19.981,23 kg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>32.355,66 kg</t>
+          <t>19.885,78 kg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>tr.44, tr.55</t>
+          <t>tr.40</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -32630,28 +32630,28 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Xà mũ trụ)</t>
+          <t>Trụ T1, T2 (Bệ móng)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 88.347,00 kg; bản vẽ 26.026,22 kg</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 18.877,75 kg; bản vẽ 32.355,66 kg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>88.347,00 kg</t>
+          <t>18.877,75 kg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26.026,22 kg</t>
+          <t>32.355,66 kg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>tr.51, tr.62</t>
+          <t>tr.44, tr.55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -32663,20 +32663,28 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
+          <t>Trụ T1, T2 (Xà mũ trụ)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Số cấu kiện cần xác nhận: Số phiến 3 S1B1 + 3 S1B2 + 9 S1G suy từ bảng tổng hợp toàn cầu tr.175 (dấu thẩm tra): 3×6.071,25 + 3×6.065,28 + 9×5.920,08 = 89.690,31 kg = 77,743 + 11,947 t — xác nhận theo mặt cắt ngang bố trí dầm.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>THAY THEO BẢN VẼ: BBS cũ 88.347,00 kg; bản vẽ 26.026,22 kg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>88.347,00 kg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>26.026,22 kg</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>tr.88, tr.91, tr.94</t>
+          <t>tr.51, tr.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -32694,19 +32702,11 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 361.596,10 kg; bản vẽ 89.690,31 kg</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>361.596,10 kg</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>89.690,31 kg</t>
-        </is>
-      </c>
+          <t>Số cấu kiện cần xác nhận: Số phiến 3 S1B1 + 3 S1B2 + 9 S1G suy từ bảng tổng hợp toàn cầu tr.175 (dấu thẩm tra): 3×6.071,25 + 3×6.065,28 + 9×5.920,08 = 89.690,31 kg = 77,743 + 11,947 t — xác nhận theo mặt cắt ngang bố trí dầm.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>tr.88, tr.91, tr.94</t>
@@ -32721,30 +32721,30 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dầm ngang (Diaphragm)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 361.596,10 kg; bản vẽ 89.690,31 kg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ø128 L=0.002 m × 525 × 1, 106.18 kg/m = 111,49 kg</t>
+          <t>361.596,10 kg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>đã loại</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>89.690,31 kg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>tr.88, tr.91, tr.94</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ø32 L=0.002 m × 1450 × 1, 114.61 kg/m = 332,37 kg</t>
+          <t>Ø128 L=0.002 m × 525 × 1, 106.18 kg/m = 111,49 kg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -32792,7 +32792,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -32802,7 +32802,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ø112 L=0.002 m × 1390 × 1, 245.97 kg/m = 683,80 kg</t>
+          <t>Ø32 L=0.002 m × 1450 × 1, 114.61 kg/m = 332,37 kg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -32835,7 +32835,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ø32 L=0.002 m × 1140 × 1, 57.64 kg/m = 131,42 kg</t>
+          <t>Ø112 L=0.002 m × 1390 × 1, 245.97 kg/m = 683,80 kg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -32868,7 +32868,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ø64 L=0.002 m × 3262 × 1, 329.85 kg/m = 2.151,94 kg</t>
+          <t>Ø32 L=0.002 m × 1140 × 1, 57.64 kg/m = 131,42 kg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -32901,7 +32901,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ø16 L=0.002 m × 2642 × 1, 66.79 kg/m = 352,92 kg</t>
+          <t>Ø64 L=0.002 m × 3262 × 1, 329.85 kg/m = 2.151,94 kg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -32922,27 +32922,27 @@
           <t>Dầm ngang (Diaphragm)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 6 dòng lỗi 3.763,93 kg); bản vẽ 2.763,12 kg</t>
+          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3.763,93 kg</t>
+          <t>Ø16 L=0.002 m × 2642 × 1, 66.79 kg/m = 352,92 kg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.763,12 kg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>tr.96</t>
-        </is>
-      </c>
+          <t>đã loại</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -32952,30 +32952,30 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bản liên tục nhiệt (Link Slab)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>Dầm ngang (Diaphragm)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 6 dòng lỗi 3.763,93 kg); bản vẽ 2.763,12 kg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ø54 L=0.002 m × 13135 × 1, 1418.58 kg/m = 37.266,10 kg</t>
+          <t>3.763,93 kg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>đã loại</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>2.763,12 kg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>tr.96</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -32990,7 +32990,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ø168 L=0.004 m × 3920 × 1, 2535.46 kg/m = 39.756,01 kg</t>
+          <t>Ø54 L=0.002 m × 13135 × 1, 1418.58 kg/m = 37.266,10 kg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -33023,7 +33023,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -33033,7 +33033,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ø260 L=0.001 m × 320 × 1, 51.33 kg/m = 16,43 kg</t>
+          <t>Ø168 L=0.004 m × 3920 × 1, 2535.46 kg/m = 39.756,01 kg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -33066,7 +33066,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ø108 L=0.002 m × 2100 × 1, 453.6 kg/m = 1.905,12 kg</t>
+          <t>Ø260 L=0.001 m × 320 × 1, 51.33 kg/m = 16,43 kg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -33087,27 +33087,27 @@
           <t>Bản liên tục nhiệt (Link Slab)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 4 dòng lỗi 78.943,65 kg); bản vẽ 8.917,94 kg</t>
+          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>78.943,65 kg</t>
+          <t>Ø108 L=0.002 m × 2100 × 1, 453.6 kg/m = 1.905,12 kg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8.917,94 kg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>tr.112</t>
-        </is>
-      </c>
+          <t>đã loại</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -33117,28 +33117,28 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gờ lan can BTCT</t>
+          <t>Bản liên tục nhiệt (Link Slab)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 1.719,70 kg; bản vẽ 20.069,02 kg</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 4 dòng lỗi 78.943,65 kg); bản vẽ 8.917,94 kg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.719,70 kg</t>
+          <t>78.943,65 kg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20.069,02 kg</t>
+          <t>8.917,94 kg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>tr.119</t>
+          <t>tr.112</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -33150,28 +33150,28 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Khe co giãn</t>
+          <t>Gờ lan can BTCT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg; bản vẽ 1.359,80 kg</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 1.719,70 kg; bản vẽ 20.069,02 kg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0,00 kg</t>
+          <t>1.719,70 kg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.359,80 kg</t>
+          <t>20.069,02 kg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>tr.121</t>
+          <t>tr.119</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -33183,28 +33183,28 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+          <t>Khe co giãn</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Tổng các trang chi tiết 108.461,59 kg ≠ bảng tổng hợp tr.175 108.884,00 kg (lệch 422,41 kg). Tr.175: D&lt;=10 10,451 t và D&gt;18 97,451 t khớp đúng 3/7/8/8 cọc; nhóm 10&lt;D&lt;=18 ghi 0,982 t nhưng các trang cọc chỉ có 0,559 t — xem PDF tr.175.</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg; bản vẽ 1.359,80 kg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>108.461,59 kg</t>
+          <t>0,00 kg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>108.884,00 kg</t>
+          <t>1.359,80 kg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -33222,14 +33222,22 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Số cấu kiện cần xác nhận: Số cọc 3/7/8/8 khớp bảng tổng hợp tr.175 (thép D&lt;=10, D&gt;18 và vữa lấp lòng 14,43 m³ = 3×0,34 + 7×0,59 + 8×0,66 + 8×0,50).</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Tổng các trang chi tiết 108.461,59 kg ≠ bảng tổng hợp tr.175 108.884,00 kg (lệch 422,41 kg). Tr.175: D&lt;=10 10,451 t và D&gt;18 97,451 t khớp đúng 3/7/8/8 cọc; nhóm 10&lt;D&lt;=18 ghi 0,982 t nhưng các trang cọc chỉ có 0,559 t — xem PDF tr.175.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>108.461,59 kg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>108.884,00 kg</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>tr.64, tr.66, tr.68, tr.70</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -33247,19 +33255,11 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 108.765,99 kg; bản vẽ 108.461,59 kg</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>108.765,99 kg</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>108.461,59 kg</t>
-        </is>
-      </c>
+          <t>Số cấu kiện cần xác nhận: Số cọc 3/7/8/8 khớp bảng tổng hợp tr.175 (thép D&lt;=10, D&gt;18 và vữa lấp lòng 14,43 m³ = 3×0,34 + 7×0,59 + 8×0,66 + 8×0,50).</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>tr.64, tr.66, tr.68, tr.70</t>
@@ -33271,27 +33271,33 @@
       <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="n">
-        <v>44</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mố M1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>OCR ghi Ø 'DB', Ø8 suy từ kg/m 0.395 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.31</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+          <t>THAY THEO BẢN VẼ: BBS cũ 108.765,99 kg; bản vẽ 108.461,59 kg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>108.765,99 kg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>108.461,59 kg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>tr.64, tr.66, tr.68, tr.70</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -33299,21 +33305,21 @@
         <v>27</v>
       </c>
       <c r="B30" t="n">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mố M2</t>
+          <t>Mố M1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>W6(T)</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>OCR ghi Ø 'DB', Ø8 suy từ kg/m 0.395 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -33340,7 +33346,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>BBS vẫn giữ thanh này để gia công (có dài và số lượng trên bản vẽ) nên BBS lớn hơn tổng bản vẽ phần này — chủ dự án quyết định và ghim</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -33353,7 +33359,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -33362,12 +33368,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>W7(T)</t>
+          <t>W6(T)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -33394,7 +33400,7 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>BBS vẫn giữ thanh này để gia công (có dài và số lượng trên bản vẽ) nên BBS lớn hơn tổng bản vẽ phần này — chủ dự án quyết định và ghim</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -33407,7 +33413,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -33416,12 +33422,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>W9(T)</t>
+          <t>W7(T)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -33448,7 +33454,7 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>BBS vẫn giữ thanh này để gia công (có dài và số lượng trên bản vẽ) nên BBS lớn hơn tổng bản vẽ phần này — chủ dự án quyết định và ghim</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -33461,7 +33467,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -33470,12 +33476,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>W9(T)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -33488,7 +33494,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -33497,12 +33503,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>n</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -33515,7 +33521,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -33524,12 +33530,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -33542,7 +33548,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -33551,12 +33557,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -33569,7 +33575,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -33578,12 +33584,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -33596,21 +33602,21 @@
         <v>38</v>
       </c>
       <c r="B41" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Bệ móng)</t>
+          <t>Mố M2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(?)</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 4) — xem PDF tr.44</t>
+          <t>OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -33623,11 +33629,11 @@
         <v>39</v>
       </c>
       <c r="B42" t="n">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Xà mũ trụ)</t>
+          <t>Trụ T1, T2 (Bệ móng)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -33637,7 +33643,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.51</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 4) — xem PDF tr.44</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -33650,7 +33656,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -33664,7 +33670,7 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.62</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.51</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -33677,21 +33683,21 @@
         <v>41</v>
       </c>
       <c r="B44" t="n">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
+          <t>Trụ T1, T2 (Xà mũ trụ)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>G6a</t>
+          <t>(?)</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.62</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -33704,7 +33710,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -33713,12 +33719,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>G6a</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -33731,7 +33737,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="n">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -33740,12 +33746,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thanh neo</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc khối lượng = 217, dài × SL × kg/m = 2.17 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.91</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -33758,7 +33764,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="n">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -33767,12 +33773,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(?)</t>
+          <t>Thanh neo</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT ?) — xem PDF tr.94</t>
+          <t>OCR đọc khối lượng = 217, dài × SL × kg/m = 2.17 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -33785,7 +33791,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -33794,12 +33800,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>(?)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.94</t>
+          <t>OCR không đọc được ký hiệu thanh (STT ?) — xem PDF tr.94</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -33812,21 +33818,21 @@
         <v>46</v>
       </c>
       <c r="B49" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dầm ngang (Diaphragm)</t>
+          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (318.54 ÷ 106.18) — xem PDF tr.96</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.94</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -33839,7 +33845,7 @@
         <v>47</v>
       </c>
       <c r="B50" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -33848,12 +33854,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (343.83 ÷ 114.61) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (318.54 ÷ 106.18) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -33866,7 +33872,7 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -33875,12 +33881,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (737.91 ÷ 245.97) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (343.83 ÷ 114.61) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -33893,7 +33899,7 @@
         <v>49</v>
       </c>
       <c r="B52" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -33902,12 +33908,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (172.92 ÷ 57.64) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (737.91 ÷ 245.97) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -33920,7 +33926,7 @@
         <v>50</v>
       </c>
       <c r="B53" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -33929,12 +33935,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (989.55 ÷ 329.85) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (172.92 ÷ 57.64) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -33947,7 +33953,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -33956,12 +33962,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (200.37 ÷ 66.79) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (989.55 ÷ 329.85) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -33974,21 +33980,21 @@
         <v>52</v>
       </c>
       <c r="B55" t="n">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bản liên tục nhiệt (Link Slab)</t>
+          <t>Dầm ngang (Diaphragm)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (2,837.16 ÷ 1,418.58) — xem PDF tr.112</t>
+          <t>hệ số 3 suy từ cột tổng (200.37 ÷ 66.79) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -34015,7 +34021,7 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>OCR ghi Ø 'D1', Ø18 suy từ kg/m 2 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (2,837.16 ÷ 1,418.58) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -34028,7 +34034,7 @@
         <v>54</v>
       </c>
       <c r="B57" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -34037,12 +34043,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (5,070.92 ÷ 2,535.46) — xem PDF tr.112</t>
+          <t>OCR ghi Ø 'D1', Ø18 suy từ kg/m 2 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -34055,7 +34061,7 @@
         <v>55</v>
       </c>
       <c r="B58" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -34064,12 +34070,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (102.66 ÷ 51.33) — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (5,070.92 ÷ 2,535.46) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -34082,7 +34088,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -34091,12 +34097,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (907.20 ÷ 453.60) — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (102.66 ÷ 51.33) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -34109,21 +34115,21 @@
         <v>57</v>
       </c>
       <c r="B60" t="n">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gờ lan can BTCT</t>
+          <t>Bản liên tục nhiệt (Link Slab)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
+          <t>hệ số 2 suy từ cột tổng (907.20 ÷ 453.60) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -34136,7 +34142,7 @@
         <v>58</v>
       </c>
       <c r="B61" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -34145,12 +34151,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (4,016.50 ÷ 211.40) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -34163,7 +34169,7 @@
         <v>59</v>
       </c>
       <c r="B62" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -34172,12 +34178,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,209.40 ÷ 116.30) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (4,016.50 ÷ 211.40) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -34190,7 +34196,7 @@
         <v>60</v>
       </c>
       <c r="B63" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -34199,12 +34205,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>G4A</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>khối lượng 1 cấu kiện trống, = dài × SL × kg/m; hệ số 19 = tổng ÷ khối lượng — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,209.40 ÷ 116.30) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -34217,7 +34223,7 @@
         <v>61</v>
       </c>
       <c r="B64" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -34226,12 +34232,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>G4B</t>
+          <t>G4A</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (85.10 ÷ dài × SL × kg/m 4.48) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>khối lượng 1 cấu kiện trống, = dài × SL × kg/m; hệ số 19 = tổng ÷ khối lượng — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -34244,7 +34250,7 @@
         <v>62</v>
       </c>
       <c r="B65" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -34253,12 +34259,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>G4C</t>
+          <t>G4B</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (139.10 ÷ dài × SL × kg/m 7.32) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (85.10 ÷ dài × SL × kg/m 4.48) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -34271,7 +34277,7 @@
         <v>63</v>
       </c>
       <c r="B66" t="n">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -34280,12 +34286,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G4C</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (139.10 ÷ dài × SL × kg/m 7.32) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -34298,7 +34304,7 @@
         <v>64</v>
       </c>
       <c r="B67" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -34307,12 +34313,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (3,898.30 ÷ 205.20) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -34325,7 +34331,7 @@
         <v>65</v>
       </c>
       <c r="B68" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -34334,12 +34340,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (1,292.30 ÷ 68.00) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (3,898.30 ÷ 205.20) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -34352,7 +34358,7 @@
         <v>66</v>
       </c>
       <c r="B69" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -34361,12 +34367,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>G7A</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,274.30 ÷ 119.70) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (1,292.30 ÷ 68.00) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -34379,7 +34385,7 @@
         <v>67</v>
       </c>
       <c r="B70" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -34388,12 +34394,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>G8A</t>
+          <t>G7A</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (57.00 ÷ 3.00) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,274.30 ÷ 119.70) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -34406,7 +34412,7 @@
         <v>68</v>
       </c>
       <c r="B71" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -34415,12 +34421,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>G8B</t>
+          <t>G8A</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (67.10 ÷ dài × SL × kg/m 3.53) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (57.00 ÷ 3.00) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -34433,7 +34439,7 @@
         <v>69</v>
       </c>
       <c r="B72" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -34442,12 +34448,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>G8C</t>
+          <t>G8B</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (91.50 ÷ dài × SL × kg/m 4.81) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (67.10 ÷ dài × SL × kg/m 3.53) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -34460,7 +34466,7 @@
         <v>70</v>
       </c>
       <c r="B73" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -34469,12 +34475,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>G8A</t>
+          <t>G8C</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (91.50 ÷ dài × SL × kg/m 4.81) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -34487,21 +34493,21 @@
         <v>71</v>
       </c>
       <c r="B74" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Khe co giãn</t>
+          <t>Gờ lan can BTCT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>G8A</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (586.67 ÷ 293.33) — xem PDF tr.121</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -34514,7 +34520,7 @@
         <v>72</v>
       </c>
       <c r="B75" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -34523,12 +34529,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (521.99 ÷ 260.99) — xem PDF tr.121</t>
+          <t>hệ số 2 suy từ cột tổng (586.67 ÷ 293.33) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -34541,7 +34547,7 @@
         <v>73</v>
       </c>
       <c r="B76" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -34550,12 +34556,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (251.14 ÷ 125.57) — xem PDF tr.121</t>
+          <t>hệ số 2 suy từ cột tổng (521.99 ÷ 260.99) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -34563,6 +34569,33 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" t="n">
+        <v>365</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Khe co giãn</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>hệ số 2 suy từ cột tổng (251.14 ÷ 125.57) — xem PDF tr.121</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/04_Thong_Ke_Thep_Chi_Tiet_BBS_396_Dong.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/04_Thong_Ke_Thep_Chi_Tiet_BBS_396_Dong.xlsx
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -21343,7 +21343,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Dầm S1B3 (dùng bảng thép S1B1) (tr.88)</t>
+          <t>Dầm S1B3 (bảng thép như S1B1) (tr.88)</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Số phiến theo chủ dự án 11/10/2026: 2 S1B1 + 3 S1B2 + 1 S1B3 + 9 S1G (khớp sơ đồ bố trí nhịp tr.75). Hồ sơ không có bảng thép riêng cho S1B3 (tr.86–94 chỉ có S1B1, S1B2, S1G) — tạm dùng bảng S1B1 tr.88; tổng 89.690,31 kg khớp tr.175 chỉ khi S1B3 = S1B1. Đối chiếu PDF bản vẽ S1B3.</t>
+          <t>Chủ dự án xác nhận 11/10/2026: 2 S1B1 + 3 S1B2 + 1 S1B3 + 9 S1G (khớp sơ đồ bố trí nhịp tr.75); S1B3 dùng bảng thép giống S1B1 (tr.88). Tổng 89.690,31 kg khớp bảng tổng hợp tr.175 (77,743 + 11,947 t).</t>
         </is>
       </c>
     </row>
@@ -34162,7 +34162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -34450,11 +34450,19 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Số cấu kiện cần xác nhận: Số phiến theo chủ dự án 11/10/2026: 2 S1B1 + 3 S1B2 + 1 S1B3 + 9 S1G (khớp sơ đồ bố trí nhịp tr.75). Hồ sơ không có bảng thép riêng cho S1B3 (tr.86–94 chỉ có S1B1, S1B2, S1G) — tạm dùng bảng S1B1 tr.88; tổng 89.690,31 kg khớp tr.175 chỉ khi S1B3 = S1B1. Đối chiếu PDF bản vẽ S1B3.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>THAY THEO BẢN VẼ: BBS cũ 361.596,10 kg; bản vẽ 89.690,31 kg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>361.596,10 kg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>89.690,31 kg</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>tr.88, tr.91, tr.88, tr.94</t>
@@ -34469,30 +34477,30 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Dầm ngang (Diaphragm)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 361.596,10 kg; bản vẽ 89.690,31 kg</t>
+          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>361.596,10 kg</t>
+          <t>Ø128 L=0.002 m × 525 × 1, 106.18 kg/m = 111,49 kg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>89.690,31 kg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>tr.88, tr.91, tr.88, tr.94</t>
-        </is>
-      </c>
+          <t>đã loại</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -34507,7 +34515,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -34517,7 +34525,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ø128 L=0.002 m × 525 × 1, 106.18 kg/m = 111,49 kg</t>
+          <t>Ø32 L=0.002 m × 1450 × 1, 114.61 kg/m = 332,37 kg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -34540,7 +34548,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -34550,7 +34558,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ø32 L=0.002 m × 1450 × 1, 114.61 kg/m = 332,37 kg</t>
+          <t>Ø112 L=0.002 m × 1390 × 1, 245.97 kg/m = 683,80 kg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -34583,7 +34591,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ø112 L=0.002 m × 1390 × 1, 245.97 kg/m = 683,80 kg</t>
+          <t>Ø32 L=0.002 m × 1140 × 1, 57.64 kg/m = 131,42 kg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -34616,7 +34624,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ø32 L=0.002 m × 1140 × 1, 57.64 kg/m = 131,42 kg</t>
+          <t>Ø64 L=0.002 m × 3262 × 1, 329.85 kg/m = 2.151,94 kg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -34649,7 +34657,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ø64 L=0.002 m × 3262 × 1, 329.85 kg/m = 2.151,94 kg</t>
+          <t>Ø16 L=0.002 m × 2642 × 1, 66.79 kg/m = 352,92 kg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -34670,27 +34678,27 @@
           <t>Dầm ngang (Diaphragm)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 6 dòng lỗi 3.763,93 kg); bản vẽ 2.763,12 kg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ø16 L=0.002 m × 2642 × 1, 66.79 kg/m = 352,92 kg</t>
+          <t>3.763,93 kg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>đã loại</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>2.763,12 kg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>tr.96</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -34700,30 +34708,30 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dầm ngang (Diaphragm)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Bản liên tục nhiệt (Link Slab)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 6 dòng lỗi 3.763,93 kg); bản vẽ 2.763,12 kg</t>
+          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.763,93 kg</t>
+          <t>Ø54 L=0.002 m × 13135 × 1, 1418.58 kg/m = 37.266,10 kg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.763,12 kg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>tr.96</t>
-        </is>
-      </c>
+          <t>đã loại</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -34738,7 +34746,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -34748,7 +34756,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ø54 L=0.002 m × 13135 × 1, 1418.58 kg/m = 37.266,10 kg</t>
+          <t>Ø168 L=0.004 m × 3920 × 1, 2535.46 kg/m = 39.756,01 kg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -34771,7 +34779,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -34781,7 +34789,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ø168 L=0.004 m × 3920 × 1, 2535.46 kg/m = 39.756,01 kg</t>
+          <t>Ø260 L=0.001 m × 320 × 1, 51.33 kg/m = 16,43 kg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -34804,7 +34812,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -34814,7 +34822,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ø260 L=0.001 m × 320 × 1, 51.33 kg/m = 16,43 kg</t>
+          <t>Ø108 L=0.002 m × 2100 × 1, 453.6 kg/m = 1.905,12 kg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -34835,27 +34843,27 @@
           <t>Bản liên tục nhiệt (Link Slab)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Dòng BBS cũ sai rõ ràng (Ø không phải thép thanh hoặc dài &lt; 50 mm) — đã loại</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 4 dòng lỗi 78.943,65 kg); bản vẽ 8.917,94 kg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ø108 L=0.002 m × 2100 × 1, 453.6 kg/m = 1.905,12 kg</t>
+          <t>78.943,65 kg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>đã loại</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>8.917,94 kg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>tr.112</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -34865,28 +34873,28 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bản liên tục nhiệt (Link Slab)</t>
+          <t>Gờ lan can BTCT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg (+ 4 dòng lỗi 78.943,65 kg); bản vẽ 8.917,94 kg</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 1.719,70 kg; bản vẽ 20.069,02 kg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>78.943,65 kg</t>
+          <t>1.719,70 kg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8.917,94 kg</t>
+          <t>20.069,02 kg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>tr.112</t>
+          <t>tr.119</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -34898,28 +34906,28 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gờ lan can BTCT</t>
+          <t>Khe co giãn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 1.719,70 kg; bản vẽ 20.069,02 kg</t>
+          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg; bản vẽ 1.359,80 kg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.719,70 kg</t>
+          <t>0,00 kg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20.069,02 kg</t>
+          <t>1.359,80 kg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>tr.119</t>
+          <t>tr.121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -34931,28 +34939,28 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Khe co giãn</t>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 0,00 kg; bản vẽ 1.359,80 kg</t>
+          <t>Tổng các trang chi tiết 108.461,59 kg ≠ bảng tổng hợp tr.175 108.884,00 kg (lệch 422,41 kg). Tr.175: D&lt;=10 10,451 t và D&gt;18 97,451 t khớp đúng 3/7/8/8 cọc; nhóm 10&lt;D&lt;=18 ghi 0,982 t nhưng các trang cọc chỉ có 0,559 t — xem PDF tr.175.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0,00 kg</t>
+          <t>108.461,59 kg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.359,80 kg</t>
+          <t>108.884,00 kg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>tr.121</t>
+          <t>tr.175</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -34970,22 +34978,14 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Tổng các trang chi tiết 108.461,59 kg ≠ bảng tổng hợp tr.175 108.884,00 kg (lệch 422,41 kg). Tr.175: D&lt;=10 10,451 t và D&gt;18 97,451 t khớp đúng 3/7/8/8 cọc; nhóm 10&lt;D&lt;=18 ghi 0,982 t nhưng các trang cọc chỉ có 0,559 t — xem PDF tr.175.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>108.461,59 kg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>108.884,00 kg</t>
-        </is>
-      </c>
+          <t>Số cấu kiện cần xác nhận: Số cọc 3/7/8/8 khớp bảng tổng hợp tr.175 (thép D&lt;=10, D&gt;18 và vữa lấp lòng 14,43 m³ = 3×0,34 + 7×0,59 + 8×0,66 + 8×0,50).</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.64, tr.66, tr.68, tr.70</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -35003,11 +35003,19 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Số cấu kiện cần xác nhận: Số cọc 3/7/8/8 khớp bảng tổng hợp tr.175 (thép D&lt;=10, D&gt;18 và vữa lấp lòng 14,43 m³ = 3×0,34 + 7×0,59 + 8×0,66 + 8×0,50).</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>THAY THEO BẢN VẼ: BBS cũ 108.765,99 kg; bản vẽ 108.461,59 kg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>108.765,99 kg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>108.461,59 kg</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>tr.64, tr.66, tr.68, tr.70</t>
@@ -35019,33 +35027,27 @@
       <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>44</v>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Mố M1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 108.765,99 kg; bản vẽ 108.461,59 kg</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>108.765,99 kg</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>108.461,59 kg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>tr.64, tr.66, tr.68, tr.70</t>
-        </is>
-      </c>
+          <t>OCR ghi Ø 'DB', Ø8 suy từ kg/m 0.395 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.31</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -35053,21 +35055,21 @@
         <v>27</v>
       </c>
       <c r="B30" t="n">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mố M1</t>
+          <t>Mố M2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>W6(T)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>OCR ghi Ø 'DB', Ø8 suy từ kg/m 0.395 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.31</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -35094,7 +35096,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -35107,7 +35109,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -35116,12 +35118,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>W6(T)</t>
+          <t>W7(T)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -35148,7 +35150,7 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -35161,7 +35163,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -35170,12 +35172,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>W7(T)</t>
+          <t>W9(T)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -35202,7 +35204,7 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -35215,7 +35217,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -35224,12 +35226,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>W9(T)</t>
+          <t>n</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
+          <t>OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -35242,7 +35244,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -35251,12 +35253,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -35269,7 +35271,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -35278,12 +35280,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -35296,7 +35298,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -35305,12 +35307,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -35323,7 +35325,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -35332,12 +35334,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -35350,21 +35352,21 @@
         <v>38</v>
       </c>
       <c r="B41" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mố M2</t>
+          <t>Trụ T1, T2 (Bệ móng)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>(?)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 4) — xem PDF tr.44</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -35377,11 +35379,11 @@
         <v>39</v>
       </c>
       <c r="B42" t="n">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Bệ móng)</t>
+          <t>Trụ T1, T2 (Xà mũ trụ)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -35391,7 +35393,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 4) — xem PDF tr.44</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.51</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -35404,7 +35406,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -35418,7 +35420,7 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.51</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.62</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -35431,21 +35433,21 @@
         <v>41</v>
       </c>
       <c r="B44" t="n">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Xà mũ trụ)</t>
+          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(?)</t>
+          <t>G6a</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.62</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -35458,7 +35460,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -35467,12 +35469,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>G6a</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -35485,7 +35487,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="n">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -35494,12 +35496,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>Thanh neo</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>OCR đọc khối lượng = 217, dài × SL × kg/m = 2.17 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -35512,7 +35514,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -35521,12 +35523,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thanh neo</t>
+          <t>G6a</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc khối lượng = 217, dài × SL × kg/m = 2.17 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.91</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -35539,7 +35541,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -35548,12 +35550,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>G6a</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -35566,7 +35568,7 @@
         <v>46</v>
       </c>
       <c r="B49" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -35575,12 +35577,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>(?)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>OCR không đọc được ký hiệu thanh (STT ?) — xem PDF tr.94</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -35593,7 +35595,7 @@
         <v>47</v>
       </c>
       <c r="B50" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -35602,12 +35604,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(?)</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT ?) — xem PDF tr.94</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.94</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -35620,21 +35622,21 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
+          <t>Dầm ngang (Diaphragm)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.94</t>
+          <t>hệ số 3 suy từ cột tổng (318.54 ÷ 106.18) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -35647,7 +35649,7 @@
         <v>49</v>
       </c>
       <c r="B52" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -35656,12 +35658,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (318.54 ÷ 106.18) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (343.83 ÷ 114.61) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -35674,7 +35676,7 @@
         <v>50</v>
       </c>
       <c r="B53" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -35683,12 +35685,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (343.83 ÷ 114.61) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (737.91 ÷ 245.97) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -35701,7 +35703,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -35710,12 +35712,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (737.91 ÷ 245.97) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (172.92 ÷ 57.64) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -35728,7 +35730,7 @@
         <v>52</v>
       </c>
       <c r="B55" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -35737,12 +35739,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (172.92 ÷ 57.64) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (989.55 ÷ 329.85) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -35755,7 +35757,7 @@
         <v>53</v>
       </c>
       <c r="B56" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -35764,12 +35766,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (989.55 ÷ 329.85) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (200.37 ÷ 66.79) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -35782,21 +35784,21 @@
         <v>54</v>
       </c>
       <c r="B57" t="n">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dầm ngang (Diaphragm)</t>
+          <t>Bản liên tục nhiệt (Link Slab)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (200.37 ÷ 66.79) — xem PDF tr.96</t>
+          <t>hệ số 2 suy từ cột tổng (2,837.16 ÷ 1,418.58) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -35823,7 +35825,7 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (2,837.16 ÷ 1,418.58) — xem PDF tr.112</t>
+          <t>OCR ghi Ø 'D1', Ø18 suy từ kg/m 2 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -35836,7 +35838,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -35845,12 +35847,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>OCR ghi Ø 'D1', Ø18 suy từ kg/m 2 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (5,070.92 ÷ 2,535.46) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -35863,7 +35865,7 @@
         <v>57</v>
       </c>
       <c r="B60" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -35872,12 +35874,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (5,070.92 ÷ 2,535.46) — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (102.66 ÷ 51.33) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -35890,7 +35892,7 @@
         <v>58</v>
       </c>
       <c r="B61" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -35899,12 +35901,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (102.66 ÷ 51.33) — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (907.20 ÷ 453.60) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -35917,21 +35919,21 @@
         <v>59</v>
       </c>
       <c r="B62" t="n">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bản liên tục nhiệt (Link Slab)</t>
+          <t>Gờ lan can BTCT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (907.20 ÷ 453.60) — xem PDF tr.112</t>
+          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -35944,7 +35946,7 @@
         <v>60</v>
       </c>
       <c r="B63" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -35953,12 +35955,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (4,016.50 ÷ 211.40) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -35971,7 +35973,7 @@
         <v>61</v>
       </c>
       <c r="B64" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -35980,12 +35982,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (4,016.50 ÷ 211.40) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,209.40 ÷ 116.30) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -35998,7 +36000,7 @@
         <v>62</v>
       </c>
       <c r="B65" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -36007,12 +36009,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G4A</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,209.40 ÷ 116.30) — xem PDF tr.119</t>
+          <t>khối lượng 1 cấu kiện trống, = dài × SL × kg/m; hệ số 19 = tổng ÷ khối lượng — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -36025,7 +36027,7 @@
         <v>63</v>
       </c>
       <c r="B66" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -36034,12 +36036,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>G4A</t>
+          <t>G4B</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>khối lượng 1 cấu kiện trống, = dài × SL × kg/m; hệ số 19 = tổng ÷ khối lượng — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (85.10 ÷ dài × SL × kg/m 4.48) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -36052,7 +36054,7 @@
         <v>64</v>
       </c>
       <c r="B67" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -36061,12 +36063,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>G4B</t>
+          <t>G4C</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (85.10 ÷ dài × SL × kg/m 4.48) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (139.10 ÷ dài × SL × kg/m 7.32) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -36079,7 +36081,7 @@
         <v>65</v>
       </c>
       <c r="B68" t="n">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -36088,12 +36090,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>G4C</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (139.10 ÷ dài × SL × kg/m 7.32) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -36106,7 +36108,7 @@
         <v>66</v>
       </c>
       <c r="B69" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -36115,12 +36117,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (3,898.30 ÷ 205.20) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -36133,7 +36135,7 @@
         <v>67</v>
       </c>
       <c r="B70" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -36142,12 +36144,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (3,898.30 ÷ 205.20) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (1,292.30 ÷ 68.00) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -36160,7 +36162,7 @@
         <v>68</v>
       </c>
       <c r="B71" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -36169,12 +36171,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G7A</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (1,292.30 ÷ 68.00) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,274.30 ÷ 119.70) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -36187,7 +36189,7 @@
         <v>69</v>
       </c>
       <c r="B72" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -36196,12 +36198,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>G7A</t>
+          <t>G8A</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,274.30 ÷ 119.70) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (57.00 ÷ 3.00) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -36214,7 +36216,7 @@
         <v>70</v>
       </c>
       <c r="B73" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -36223,12 +36225,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>G8A</t>
+          <t>G8B</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (57.00 ÷ 3.00) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (67.10 ÷ dài × SL × kg/m 3.53) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -36241,7 +36243,7 @@
         <v>71</v>
       </c>
       <c r="B74" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -36250,12 +36252,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>G8B</t>
+          <t>G8C</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (67.10 ÷ dài × SL × kg/m 3.53) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (91.50 ÷ dài × SL × kg/m 4.81) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -36268,7 +36270,7 @@
         <v>72</v>
       </c>
       <c r="B75" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -36277,12 +36279,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>G8C</t>
+          <t>G8A</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (91.50 ÷ dài × SL × kg/m 4.81) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -36295,21 +36297,21 @@
         <v>73</v>
       </c>
       <c r="B76" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gờ lan can BTCT</t>
+          <t>Khe co giãn</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>G8A</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
+          <t>hệ số 2 suy từ cột tổng (586.67 ÷ 293.33) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -36322,7 +36324,7 @@
         <v>74</v>
       </c>
       <c r="B77" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -36331,12 +36333,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (586.67 ÷ 293.33) — xem PDF tr.121</t>
+          <t>hệ số 2 suy từ cột tổng (521.99 ÷ 260.99) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -36349,7 +36351,7 @@
         <v>75</v>
       </c>
       <c r="B78" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -36358,12 +36360,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (521.99 ÷ 260.99) — xem PDF tr.121</t>
+          <t>hệ số 2 suy từ cột tổng (251.14 ÷ 125.57) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -36371,33 +36373,6 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>76</v>
-      </c>
-      <c r="B79" t="n">
-        <v>388</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Khe co giãn</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>hệ số 2 suy từ cột tổng (251.14 ÷ 125.57) — xem PDF tr.121</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/04_Thong_Ke_Thep_Chi_Tiet_BBS_396_Dong.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/02_XUONG_TIEN_CHE_COT_THEP/04_Thong_Ke_Thep_Chi_Tiet_BBS_396_Dong.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:R455"/>
+  <dimension ref="A2:R459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -28882,7 +28882,7 @@
       </c>
       <c r="R390" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -28954,7 +28954,7 @@
       </c>
       <c r="R391" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29026,7 +29026,7 @@
       </c>
       <c r="R392" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="R393" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29170,7 +29170,7 @@
       </c>
       <c r="R394" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29242,7 +29242,7 @@
       </c>
       <c r="R395" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29314,7 +29314,7 @@
       </c>
       <c r="R396" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="R397" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29458,7 +29458,7 @@
       </c>
       <c r="R398" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29530,7 +29530,7 @@
       </c>
       <c r="R399" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29602,7 +29602,7 @@
       </c>
       <c r="R400" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29674,7 +29674,7 @@
       </c>
       <c r="R401" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29746,7 +29746,7 @@
       </c>
       <c r="R402" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29761,31 +29761,31 @@
       </c>
       <c r="C403" s="5" t="inlineStr">
         <is>
-          <t>Cọc mố M2 L=36m (tr.66)</t>
+          <t>Cọc mố M1 L=20m (tr.64)</t>
         </is>
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E403" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F403" s="5" t="inlineStr">
         <is>
-          <t>CB240-T</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="G403" s="5" t="inlineStr"/>
       <c r="H403" s="5" t="n">
-        <v>96.887</v>
+        <v>2.604</v>
       </c>
       <c r="I403" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J403" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K403" s="5">
         <f>I403*J403</f>
@@ -29796,7 +29796,7 @@
         <v/>
       </c>
       <c r="M403" s="5" t="n">
-        <v>0.617</v>
+        <v>1.578</v>
       </c>
       <c r="N403" s="5">
         <f>L403*M403</f>
@@ -29808,17 +29808,17 @@
       </c>
       <c r="P403" s="5" t="inlineStr">
         <is>
-          <t>D&lt;=10mm</t>
+          <t>10&lt;D&lt;=18mm</t>
         </is>
       </c>
       <c r="Q403" s="5" t="inlineStr">
         <is>
-          <t>Theo bản vẽ thẩm định tr.66</t>
+          <t>Theo bản vẽ thẩm định tr.64</t>
         </is>
       </c>
       <c r="R403" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.64 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg) | thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.64</t>
         </is>
       </c>
     </row>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>P1A</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E404" s="5" t="n">
@@ -29851,7 +29851,7 @@
       </c>
       <c r="G404" s="5" t="inlineStr"/>
       <c r="H404" s="5" t="n">
-        <v>390.776</v>
+        <v>96.887</v>
       </c>
       <c r="I404" s="5" t="n">
         <v>1</v>
@@ -29890,7 +29890,7 @@
       </c>
       <c r="R404" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>P1B</t>
+          <t>P1A</t>
         </is>
       </c>
       <c r="E405" s="5" t="n">
@@ -29923,7 +29923,7 @@
       </c>
       <c r="G405" s="5" t="inlineStr"/>
       <c r="H405" s="5" t="n">
-        <v>164.938</v>
+        <v>390.776</v>
       </c>
       <c r="I405" s="5" t="n">
         <v>1</v>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="R405" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -29982,7 +29982,7 @@
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>P1C</t>
+          <t>P1B</t>
         </is>
       </c>
       <c r="E406" s="5" t="n">
@@ -29995,10 +29995,10 @@
       </c>
       <c r="G406" s="5" t="inlineStr"/>
       <c r="H406" s="5" t="n">
-        <v>3.592</v>
+        <v>164.938</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J406" s="5" t="n">
         <v>7</v>
@@ -30034,7 +30034,7 @@
       </c>
       <c r="R406" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>P1D</t>
+          <t>P1C</t>
         </is>
       </c>
       <c r="E407" s="5" t="n">
@@ -30067,10 +30067,10 @@
       </c>
       <c r="G407" s="5" t="inlineStr"/>
       <c r="H407" s="5" t="n">
-        <v>23.007</v>
+        <v>3.592</v>
       </c>
       <c r="I407" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J407" s="5" t="n">
         <v>7</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="R407" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30126,23 +30126,23 @@
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>P2A</t>
+          <t>P1D</t>
         </is>
       </c>
       <c r="E408" s="5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F408" s="5" t="inlineStr">
         <is>
-          <t>CB400-V</t>
+          <t>CB240-T</t>
         </is>
       </c>
       <c r="G408" s="5" t="inlineStr"/>
       <c r="H408" s="5" t="n">
-        <v>2.966</v>
+        <v>23.007</v>
       </c>
       <c r="I408" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J408" s="5" t="n">
         <v>7</v>
@@ -30156,7 +30156,7 @@
         <v/>
       </c>
       <c r="M408" s="5" t="n">
-        <v>4.834</v>
+        <v>0.617</v>
       </c>
       <c r="N408" s="5">
         <f>L408*M408</f>
@@ -30168,7 +30168,7 @@
       </c>
       <c r="P408" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>D&lt;=10mm</t>
         </is>
       </c>
       <c r="Q408" s="5" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="R408" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30198,11 +30198,11 @@
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>P2B</t>
+          <t>P2A</t>
         </is>
       </c>
       <c r="E409" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F409" s="5" t="inlineStr">
         <is>
@@ -30211,10 +30211,10 @@
       </c>
       <c r="G409" s="5" t="inlineStr"/>
       <c r="H409" s="5" t="n">
-        <v>2.985</v>
+        <v>2.966</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J409" s="5" t="n">
         <v>7</v>
@@ -30228,7 +30228,7 @@
         <v/>
       </c>
       <c r="M409" s="5" t="n">
-        <v>3.853</v>
+        <v>4.834</v>
       </c>
       <c r="N409" s="5">
         <f>L409*M409</f>
@@ -30250,7 +30250,7 @@
       </c>
       <c r="R409" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30270,11 +30270,11 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2B</t>
         </is>
       </c>
       <c r="E410" s="5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F410" s="5" t="inlineStr">
         <is>
@@ -30283,10 +30283,10 @@
       </c>
       <c r="G410" s="5" t="inlineStr"/>
       <c r="H410" s="5" t="n">
-        <v>10.7</v>
+        <v>2.985</v>
       </c>
       <c r="I410" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J410" s="5" t="n">
         <v>7</v>
@@ -30300,7 +30300,7 @@
         <v/>
       </c>
       <c r="M410" s="5" t="n">
-        <v>4.834</v>
+        <v>3.853</v>
       </c>
       <c r="N410" s="5">
         <f>L410*M410</f>
@@ -30322,7 +30322,7 @@
       </c>
       <c r="R410" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30342,7 +30342,7 @@
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E411" s="5" t="n">
@@ -30355,7 +30355,7 @@
       </c>
       <c r="G411" s="5" t="inlineStr"/>
       <c r="H411" s="5" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="I411" s="5" t="n">
         <v>12</v>
@@ -30394,7 +30394,7 @@
       </c>
       <c r="R411" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30414,11 +30414,11 @@
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E412" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F412" s="5" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>11.7</v>
       </c>
       <c r="I412" s="5" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J412" s="5" t="n">
         <v>7</v>
@@ -30444,7 +30444,7 @@
         <v/>
       </c>
       <c r="M412" s="5" t="n">
-        <v>3.853</v>
+        <v>4.834</v>
       </c>
       <c r="N412" s="5">
         <f>L412*M412</f>
@@ -30466,7 +30466,7 @@
       </c>
       <c r="R412" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E413" s="5" t="n">
@@ -30499,10 +30499,10 @@
       </c>
       <c r="G413" s="5" t="inlineStr"/>
       <c r="H413" s="5" t="n">
-        <v>5.153</v>
+        <v>11.7</v>
       </c>
       <c r="I413" s="5" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="J413" s="5" t="n">
         <v>7</v>
@@ -30538,7 +30538,7 @@
       </c>
       <c r="R413" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30558,7 @@
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E414" s="5" t="n">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="G414" s="5" t="inlineStr"/>
       <c r="H414" s="5" t="n">
-        <v>6.153</v>
+        <v>5.153</v>
       </c>
       <c r="I414" s="5" t="n">
         <v>12</v>
@@ -30610,7 +30610,7 @@
       </c>
       <c r="R414" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30630,11 +30630,11 @@
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E415" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F415" s="5" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
       </c>
       <c r="G415" s="5" t="inlineStr"/>
       <c r="H415" s="5" t="n">
-        <v>0.647</v>
+        <v>6.153</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J415" s="5" t="n">
         <v>7</v>
@@ -30660,7 +30660,7 @@
         <v/>
       </c>
       <c r="M415" s="5" t="n">
-        <v>0.888</v>
+        <v>3.853</v>
       </c>
       <c r="N415" s="5">
         <f>L415*M415</f>
@@ -30672,7 +30672,7 @@
       </c>
       <c r="P415" s="5" t="inlineStr">
         <is>
-          <t>10&lt;D&lt;=18mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q415" s="5" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="R415" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30702,7 +30702,7 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E416" s="5" t="n">
@@ -30715,10 +30715,10 @@
       </c>
       <c r="G416" s="5" t="inlineStr"/>
       <c r="H416" s="5" t="n">
-        <v>0.379</v>
+        <v>0.647</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J416" s="5" t="n">
         <v>7</v>
@@ -30754,7 +30754,7 @@
       </c>
       <c r="R416" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30774,11 +30774,11 @@
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E417" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F417" s="5" t="inlineStr">
         <is>
@@ -30787,10 +30787,10 @@
       </c>
       <c r="G417" s="5" t="inlineStr"/>
       <c r="H417" s="5" t="n">
-        <v>2.057</v>
+        <v>0.379</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="J417" s="5" t="n">
         <v>7</v>
@@ -30804,7 +30804,7 @@
         <v/>
       </c>
       <c r="M417" s="5" t="n">
-        <v>2.466</v>
+        <v>0.888</v>
       </c>
       <c r="N417" s="5">
         <f>L417*M417</f>
@@ -30816,7 +30816,7 @@
       </c>
       <c r="P417" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>10&lt;D&lt;=18mm</t>
         </is>
       </c>
       <c r="Q417" s="5" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="R417" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30846,7 +30846,7 @@
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E418" s="5" t="n">
@@ -30859,10 +30859,10 @@
       </c>
       <c r="G418" s="5" t="inlineStr"/>
       <c r="H418" s="5" t="n">
-        <v>0.583</v>
+        <v>2.057</v>
       </c>
       <c r="I418" s="5" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="J418" s="5" t="n">
         <v>7</v>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="R418" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30913,31 +30913,31 @@
       </c>
       <c r="C419" s="5" t="inlineStr">
         <is>
-          <t>Cọc trụ T1 L=40m (tr.68)</t>
+          <t>Cọc mố M2 L=36m (tr.66)</t>
         </is>
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E419" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F419" s="5" t="inlineStr">
         <is>
-          <t>CB240-T</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="G419" s="5" t="inlineStr"/>
       <c r="H419" s="5" t="n">
-        <v>96.604</v>
+        <v>0.583</v>
       </c>
       <c r="I419" s="5" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J419" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K419" s="5">
         <f>I419*J419</f>
@@ -30948,7 +30948,7 @@
         <v/>
       </c>
       <c r="M419" s="5" t="n">
-        <v>0.617</v>
+        <v>2.466</v>
       </c>
       <c r="N419" s="5">
         <f>L419*M419</f>
@@ -30960,17 +30960,17 @@
       </c>
       <c r="P419" s="5" t="inlineStr">
         <is>
-          <t>D&lt;=10mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q419" s="5" t="inlineStr">
         <is>
-          <t>Theo bản vẽ thẩm định tr.68</t>
+          <t>Theo bản vẽ thẩm định tr.66</t>
         </is>
       </c>
       <c r="R419" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -30985,31 +30985,31 @@
       </c>
       <c r="C420" s="5" t="inlineStr">
         <is>
-          <t>Cọc trụ T1 L=40m (tr.68)</t>
+          <t>Cọc mố M2 L=36m (tr.66)</t>
         </is>
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>P1A</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E420" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F420" s="5" t="inlineStr">
         <is>
-          <t>CB240-T</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="G420" s="5" t="inlineStr"/>
       <c r="H420" s="5" t="n">
-        <v>389.636</v>
+        <v>2.484</v>
       </c>
       <c r="I420" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J420" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K420" s="5">
         <f>I420*J420</f>
@@ -31020,7 +31020,7 @@
         <v/>
       </c>
       <c r="M420" s="5" t="n">
-        <v>0.617</v>
+        <v>1.578</v>
       </c>
       <c r="N420" s="5">
         <f>L420*M420</f>
@@ -31032,17 +31032,17 @@
       </c>
       <c r="P420" s="5" t="inlineStr">
         <is>
-          <t>D&lt;=10mm</t>
+          <t>10&lt;D&lt;=18mm</t>
         </is>
       </c>
       <c r="Q420" s="5" t="inlineStr">
         <is>
-          <t>Theo bản vẽ thẩm định tr.68</t>
+          <t>Theo bản vẽ thẩm định tr.66</t>
         </is>
       </c>
       <c r="R420" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.66 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg) | thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.66 | số thanh trống trên OCR, suy = khối lượng ÷ (dài × kg/m) = 4 — xem PDF tr.66</t>
         </is>
       </c>
     </row>
@@ -31062,7 +31062,7 @@
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>P1B</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E421" s="5" t="n">
@@ -31075,7 +31075,7 @@
       </c>
       <c r="G421" s="5" t="inlineStr"/>
       <c r="H421" s="5" t="n">
-        <v>206.981</v>
+        <v>96.604</v>
       </c>
       <c r="I421" s="5" t="n">
         <v>1</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="R421" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31134,7 +31134,7 @@
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>P1C</t>
+          <t>P1A</t>
         </is>
       </c>
       <c r="E422" s="5" t="n">
@@ -31147,10 +31147,10 @@
       </c>
       <c r="G422" s="5" t="inlineStr"/>
       <c r="H422" s="5" t="n">
-        <v>3.592</v>
+        <v>389.636</v>
       </c>
       <c r="I422" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J422" s="5" t="n">
         <v>8</v>
@@ -31186,7 +31186,7 @@
       </c>
       <c r="R422" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>P1D</t>
+          <t>P1B</t>
         </is>
       </c>
       <c r="E423" s="5" t="n">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="G423" s="5" t="inlineStr"/>
       <c r="H423" s="5" t="n">
-        <v>19.721</v>
+        <v>206.981</v>
       </c>
       <c r="I423" s="5" t="n">
         <v>1</v>
@@ -31258,7 +31258,7 @@
       </c>
       <c r="R423" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31278,23 +31278,23 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>P2B</t>
+          <t>P1C</t>
         </is>
       </c>
       <c r="E424" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F424" s="5" t="inlineStr">
         <is>
-          <t>CB400-V</t>
+          <t>CB240-T</t>
         </is>
       </c>
       <c r="G424" s="5" t="inlineStr"/>
       <c r="H424" s="5" t="n">
-        <v>2.985</v>
+        <v>3.592</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J424" s="5" t="n">
         <v>8</v>
@@ -31308,7 +31308,7 @@
         <v/>
       </c>
       <c r="M424" s="5" t="n">
-        <v>3.853</v>
+        <v>0.617</v>
       </c>
       <c r="N424" s="5">
         <f>L424*M424</f>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="P424" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>D&lt;=10mm</t>
         </is>
       </c>
       <c r="Q424" s="5" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="R424" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31350,23 +31350,23 @@
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1D</t>
         </is>
       </c>
       <c r="E425" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F425" s="5" t="inlineStr">
         <is>
-          <t>CB400-V</t>
+          <t>CB240-T</t>
         </is>
       </c>
       <c r="G425" s="5" t="inlineStr"/>
       <c r="H425" s="5" t="n">
-        <v>10.7</v>
+        <v>19.721</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J425" s="5" t="n">
         <v>8</v>
@@ -31380,7 +31380,7 @@
         <v/>
       </c>
       <c r="M425" s="5" t="n">
-        <v>3.853</v>
+        <v>0.617</v>
       </c>
       <c r="N425" s="5">
         <f>L425*M425</f>
@@ -31392,7 +31392,7 @@
       </c>
       <c r="P425" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>D&lt;=10mm</t>
         </is>
       </c>
       <c r="Q425" s="5" t="inlineStr">
@@ -31402,7 +31402,7 @@
       </c>
       <c r="R425" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31422,7 +31422,7 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2B</t>
         </is>
       </c>
       <c r="E426" s="5" t="n">
@@ -31435,10 +31435,10 @@
       </c>
       <c r="G426" s="5" t="inlineStr"/>
       <c r="H426" s="5" t="n">
-        <v>11.7</v>
+        <v>2.985</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="J426" s="5" t="n">
         <v>8</v>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="R426" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31494,7 @@
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E427" s="5" t="n">
@@ -31507,7 +31507,7 @@
       </c>
       <c r="G427" s="5" t="inlineStr"/>
       <c r="H427" s="5" t="n">
-        <v>9.032999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="I427" s="5" t="n">
         <v>12</v>
@@ -31546,7 +31546,7 @@
       </c>
       <c r="R427" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31566,7 +31566,7 @@
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E428" s="5" t="n">
@@ -31579,10 +31579,10 @@
       </c>
       <c r="G428" s="5" t="inlineStr"/>
       <c r="H428" s="5" t="n">
-        <v>10.033</v>
+        <v>11.7</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="J428" s="5" t="n">
         <v>8</v>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="R428" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31638,11 +31638,11 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E429" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F429" s="5" t="inlineStr">
         <is>
@@ -31651,10 +31651,10 @@
       </c>
       <c r="G429" s="5" t="inlineStr"/>
       <c r="H429" s="5" t="n">
-        <v>0.647</v>
+        <v>9.032999999999999</v>
       </c>
       <c r="I429" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J429" s="5" t="n">
         <v>8</v>
@@ -31668,7 +31668,7 @@
         <v/>
       </c>
       <c r="M429" s="5" t="n">
-        <v>0.888</v>
+        <v>3.853</v>
       </c>
       <c r="N429" s="5">
         <f>L429*M429</f>
@@ -31680,7 +31680,7 @@
       </c>
       <c r="P429" s="5" t="inlineStr">
         <is>
-          <t>10&lt;D&lt;=18mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q429" s="5" t="inlineStr">
@@ -31690,7 +31690,7 @@
       </c>
       <c r="R429" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31710,11 +31710,11 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E430" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F430" s="5" t="inlineStr">
         <is>
@@ -31723,10 +31723,10 @@
       </c>
       <c r="G430" s="5" t="inlineStr"/>
       <c r="H430" s="5" t="n">
-        <v>0.379</v>
+        <v>10.033</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J430" s="5" t="n">
         <v>8</v>
@@ -31740,7 +31740,7 @@
         <v/>
       </c>
       <c r="M430" s="5" t="n">
-        <v>0.888</v>
+        <v>3.853</v>
       </c>
       <c r="N430" s="5">
         <f>L430*M430</f>
@@ -31752,7 +31752,7 @@
       </c>
       <c r="P430" s="5" t="inlineStr">
         <is>
-          <t>10&lt;D&lt;=18mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q430" s="5" t="inlineStr">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="R430" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31782,11 +31782,11 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E431" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F431" s="5" t="inlineStr">
         <is>
@@ -31795,10 +31795,10 @@
       </c>
       <c r="G431" s="5" t="inlineStr"/>
       <c r="H431" s="5" t="n">
-        <v>2.057</v>
+        <v>0.647</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J431" s="5" t="n">
         <v>8</v>
@@ -31812,7 +31812,7 @@
         <v/>
       </c>
       <c r="M431" s="5" t="n">
-        <v>2.466</v>
+        <v>0.888</v>
       </c>
       <c r="N431" s="5">
         <f>L431*M431</f>
@@ -31824,7 +31824,7 @@
       </c>
       <c r="P431" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>10&lt;D&lt;=18mm</t>
         </is>
       </c>
       <c r="Q431" s="5" t="inlineStr">
@@ -31834,7 +31834,7 @@
       </c>
       <c r="R431" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31854,11 +31854,11 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E432" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F432" s="5" t="inlineStr">
         <is>
@@ -31867,10 +31867,10 @@
       </c>
       <c r="G432" s="5" t="inlineStr"/>
       <c r="H432" s="5" t="n">
-        <v>0.583</v>
+        <v>0.379</v>
       </c>
       <c r="I432" s="5" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="J432" s="5" t="n">
         <v>8</v>
@@ -31884,7 +31884,7 @@
         <v/>
       </c>
       <c r="M432" s="5" t="n">
-        <v>2.466</v>
+        <v>0.888</v>
       </c>
       <c r="N432" s="5">
         <f>L432*M432</f>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="P432" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>10&lt;D&lt;=18mm</t>
         </is>
       </c>
       <c r="Q432" s="5" t="inlineStr">
@@ -31906,7 +31906,7 @@
       </c>
       <c r="R432" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31921,25 +31921,25 @@
       </c>
       <c r="C433" s="5" t="inlineStr">
         <is>
-          <t>Cọc trụ T2 L=30m (tr.70)</t>
+          <t>Cọc trụ T1 L=40m (tr.68)</t>
         </is>
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E433" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F433" s="5" t="inlineStr">
         <is>
-          <t>CB240-T</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="G433" s="5" t="inlineStr"/>
       <c r="H433" s="5" t="n">
-        <v>96.604</v>
+        <v>2.057</v>
       </c>
       <c r="I433" s="5" t="n">
         <v>1</v>
@@ -31956,7 +31956,7 @@
         <v/>
       </c>
       <c r="M433" s="5" t="n">
-        <v>0.617</v>
+        <v>2.466</v>
       </c>
       <c r="N433" s="5">
         <f>L433*M433</f>
@@ -31968,17 +31968,17 @@
       </c>
       <c r="P433" s="5" t="inlineStr">
         <is>
-          <t>D&lt;=10mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q433" s="5" t="inlineStr">
         <is>
-          <t>Theo bản vẽ thẩm định tr.70</t>
+          <t>Theo bản vẽ thẩm định tr.68</t>
         </is>
       </c>
       <c r="R433" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -31993,28 +31993,28 @@
       </c>
       <c r="C434" s="5" t="inlineStr">
         <is>
-          <t>Cọc trụ T2 L=30m (tr.70)</t>
+          <t>Cọc trụ T1 L=40m (tr.68)</t>
         </is>
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>P1A</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E434" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F434" s="5" t="inlineStr">
         <is>
-          <t>CB240-T</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="G434" s="5" t="inlineStr"/>
       <c r="H434" s="5" t="n">
-        <v>389.636</v>
+        <v>0.583</v>
       </c>
       <c r="I434" s="5" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J434" s="5" t="n">
         <v>8</v>
@@ -32028,7 +32028,7 @@
         <v/>
       </c>
       <c r="M434" s="5" t="n">
-        <v>0.617</v>
+        <v>2.466</v>
       </c>
       <c r="N434" s="5">
         <f>L434*M434</f>
@@ -32040,17 +32040,17 @@
       </c>
       <c r="P434" s="5" t="inlineStr">
         <is>
-          <t>D&lt;=10mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q434" s="5" t="inlineStr">
         <is>
-          <t>Theo bản vẽ thẩm định tr.70</t>
+          <t>Theo bản vẽ thẩm định tr.68</t>
         </is>
       </c>
       <c r="R434" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32065,28 +32065,28 @@
       </c>
       <c r="C435" s="5" t="inlineStr">
         <is>
-          <t>Cọc trụ T2 L=30m (tr.70)</t>
+          <t>Cọc trụ T1 L=40m (tr.68)</t>
         </is>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>P1B</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E435" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F435" s="5" t="inlineStr">
         <is>
-          <t>CB240-T</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="G435" s="5" t="inlineStr"/>
       <c r="H435" s="5" t="n">
-        <v>100.256</v>
+        <v>2.604</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J435" s="5" t="n">
         <v>8</v>
@@ -32100,7 +32100,7 @@
         <v/>
       </c>
       <c r="M435" s="5" t="n">
-        <v>0.617</v>
+        <v>1.578</v>
       </c>
       <c r="N435" s="5">
         <f>L435*M435</f>
@@ -32112,17 +32112,17 @@
       </c>
       <c r="P435" s="5" t="inlineStr">
         <is>
-          <t>D&lt;=10mm</t>
+          <t>10&lt;D&lt;=18mm</t>
         </is>
       </c>
       <c r="Q435" s="5" t="inlineStr">
         <is>
-          <t>Theo bản vẽ thẩm định tr.70</t>
+          <t>Theo bản vẽ thẩm định tr.68</t>
         </is>
       </c>
       <c r="R435" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.68 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg) | thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.68 | số thanh trống trên OCR, suy = khối lượng ÷ (dài × kg/m) = 4 — xem PDF tr.68</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>P1C</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E436" s="5" t="n">
@@ -32155,10 +32155,10 @@
       </c>
       <c r="G436" s="5" t="inlineStr"/>
       <c r="H436" s="5" t="n">
-        <v>3.592</v>
+        <v>96.604</v>
       </c>
       <c r="I436" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J436" s="5" t="n">
         <v>8</v>
@@ -32194,7 +32194,7 @@
       </c>
       <c r="R436" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32214,7 +32214,7 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>P1D</t>
+          <t>P1A</t>
         </is>
       </c>
       <c r="E437" s="5" t="n">
@@ -32227,7 +32227,7 @@
       </c>
       <c r="G437" s="5" t="inlineStr"/>
       <c r="H437" s="5" t="n">
-        <v>19.721</v>
+        <v>389.636</v>
       </c>
       <c r="I437" s="5" t="n">
         <v>1</v>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="R437" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32286,23 +32286,23 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>P2B</t>
+          <t>P1B</t>
         </is>
       </c>
       <c r="E438" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F438" s="5" t="inlineStr">
         <is>
-          <t>CB400-V</t>
+          <t>CB240-T</t>
         </is>
       </c>
       <c r="G438" s="5" t="inlineStr"/>
       <c r="H438" s="5" t="n">
-        <v>2.985</v>
+        <v>100.256</v>
       </c>
       <c r="I438" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J438" s="5" t="n">
         <v>8</v>
@@ -32316,7 +32316,7 @@
         <v/>
       </c>
       <c r="M438" s="5" t="n">
-        <v>3.853</v>
+        <v>0.617</v>
       </c>
       <c r="N438" s="5">
         <f>L438*M438</f>
@@ -32328,7 +32328,7 @@
       </c>
       <c r="P438" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>D&lt;=10mm</t>
         </is>
       </c>
       <c r="Q438" s="5" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="R438" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32358,23 +32358,23 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1C</t>
         </is>
       </c>
       <c r="E439" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F439" s="5" t="inlineStr">
         <is>
-          <t>CB400-V</t>
+          <t>CB240-T</t>
         </is>
       </c>
       <c r="G439" s="5" t="inlineStr"/>
       <c r="H439" s="5" t="n">
-        <v>10.7</v>
+        <v>3.592</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J439" s="5" t="n">
         <v>8</v>
@@ -32388,7 +32388,7 @@
         <v/>
       </c>
       <c r="M439" s="5" t="n">
-        <v>3.853</v>
+        <v>0.617</v>
       </c>
       <c r="N439" s="5">
         <f>L439*M439</f>
@@ -32400,7 +32400,7 @@
       </c>
       <c r="P439" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>D&lt;=10mm</t>
         </is>
       </c>
       <c r="Q439" s="5" t="inlineStr">
@@ -32410,7 +32410,7 @@
       </c>
       <c r="R439" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32430,23 +32430,23 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1D</t>
         </is>
       </c>
       <c r="E440" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F440" s="5" t="inlineStr">
         <is>
-          <t>CB400-V</t>
+          <t>CB240-T</t>
         </is>
       </c>
       <c r="G440" s="5" t="inlineStr"/>
       <c r="H440" s="5" t="n">
-        <v>11.7</v>
+        <v>19.721</v>
       </c>
       <c r="I440" s="5" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J440" s="5" t="n">
         <v>8</v>
@@ -32460,7 +32460,7 @@
         <v/>
       </c>
       <c r="M440" s="5" t="n">
-        <v>3.853</v>
+        <v>0.617</v>
       </c>
       <c r="N440" s="5">
         <f>L440*M440</f>
@@ -32472,7 +32472,7 @@
       </c>
       <c r="P440" s="5" t="inlineStr">
         <is>
-          <t>D&gt;18mm</t>
+          <t>D&lt;=10mm</t>
         </is>
       </c>
       <c r="Q440" s="5" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="R440" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32502,7 +32502,7 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P2B</t>
         </is>
       </c>
       <c r="E441" s="5" t="n">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="G441" s="5" t="inlineStr"/>
       <c r="H441" s="5" t="n">
-        <v>9.733000000000001</v>
+        <v>2.985</v>
       </c>
       <c r="I441" s="5" t="n">
         <v>12</v>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="R441" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E442" s="5" t="n">
@@ -32587,7 +32587,7 @@
       </c>
       <c r="G442" s="5" t="inlineStr"/>
       <c r="H442" s="5" t="n">
-        <v>10.733</v>
+        <v>10.7</v>
       </c>
       <c r="I442" s="5" t="n">
         <v>12</v>
@@ -32626,7 +32626,7 @@
       </c>
       <c r="R442" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32646,11 +32646,11 @@
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E443" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F443" s="5" t="inlineStr">
         <is>
@@ -32659,10 +32659,10 @@
       </c>
       <c r="G443" s="5" t="inlineStr"/>
       <c r="H443" s="5" t="n">
-        <v>0.647</v>
+        <v>11.7</v>
       </c>
       <c r="I443" s="5" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J443" s="5" t="n">
         <v>8</v>
@@ -32676,7 +32676,7 @@
         <v/>
       </c>
       <c r="M443" s="5" t="n">
-        <v>0.888</v>
+        <v>3.853</v>
       </c>
       <c r="N443" s="5">
         <f>L443*M443</f>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="P443" s="5" t="inlineStr">
         <is>
-          <t>10&lt;D&lt;=18mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q443" s="5" t="inlineStr">
@@ -32698,7 +32698,7 @@
       </c>
       <c r="R443" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32718,11 +32718,11 @@
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E444" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F444" s="5" t="inlineStr">
         <is>
@@ -32731,10 +32731,10 @@
       </c>
       <c r="G444" s="5" t="inlineStr"/>
       <c r="H444" s="5" t="n">
-        <v>0.379</v>
+        <v>9.733000000000001</v>
       </c>
       <c r="I444" s="5" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J444" s="5" t="n">
         <v>8</v>
@@ -32748,7 +32748,7 @@
         <v/>
       </c>
       <c r="M444" s="5" t="n">
-        <v>0.888</v>
+        <v>3.853</v>
       </c>
       <c r="N444" s="5">
         <f>L444*M444</f>
@@ -32760,7 +32760,7 @@
       </c>
       <c r="P444" s="5" t="inlineStr">
         <is>
-          <t>10&lt;D&lt;=18mm</t>
+          <t>D&gt;18mm</t>
         </is>
       </c>
       <c r="Q444" s="5" t="inlineStr">
@@ -32770,7 +32770,7 @@
       </c>
       <c r="R444" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32790,11 +32790,11 @@
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E445" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F445" s="5" t="inlineStr">
         <is>
@@ -32803,10 +32803,10 @@
       </c>
       <c r="G445" s="5" t="inlineStr"/>
       <c r="H445" s="5" t="n">
-        <v>2.057</v>
+        <v>10.733</v>
       </c>
       <c r="I445" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J445" s="5" t="n">
         <v>8</v>
@@ -32820,7 +32820,7 @@
         <v/>
       </c>
       <c r="M445" s="5" t="n">
-        <v>2.466</v>
+        <v>3.853</v>
       </c>
       <c r="N445" s="5">
         <f>L445*M445</f>
@@ -32842,7 +32842,7 @@
       </c>
       <c r="R445" s="5" t="inlineStr">
         <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
         </is>
       </c>
     </row>
@@ -32862,11 +32862,11 @@
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E446" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F446" s="5" t="inlineStr">
         <is>
@@ -32875,10 +32875,10 @@
       </c>
       <c r="G446" s="5" t="inlineStr"/>
       <c r="H446" s="5" t="n">
-        <v>0.583</v>
+        <v>0.647</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J446" s="5" t="n">
         <v>8</v>
@@ -32892,7 +32892,7 @@
         <v/>
       </c>
       <c r="M446" s="5" t="n">
-        <v>2.466</v>
+        <v>0.888</v>
       </c>
       <c r="N446" s="5">
         <f>L446*M446</f>
@@ -32904,152 +32904,440 @@
       </c>
       <c r="P446" s="5" t="inlineStr">
         <is>
+          <t>10&lt;D&lt;=18mm</t>
+        </is>
+      </c>
+      <c r="Q446" s="5" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ thẩm định tr.70</t>
+        </is>
+      </c>
+      <c r="R446" s="5" t="inlineStr">
+        <is>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="5" t="n">
+        <v>438</v>
+      </c>
+      <c r="B447" s="5" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>Cọc trụ T2 L=30m (tr.70)</t>
+        </is>
+      </c>
+      <c r="D447" s="5" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="E447" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F447" s="5" t="inlineStr">
+        <is>
+          <t>CB400-V</t>
+        </is>
+      </c>
+      <c r="G447" s="5" t="inlineStr"/>
+      <c r="H447" s="5" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="I447" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="J447" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K447" s="5">
+        <f>I447*J447</f>
+        <v/>
+      </c>
+      <c r="L447" s="5">
+        <f>H447*K447</f>
+        <v/>
+      </c>
+      <c r="M447" s="5" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="N447" s="5">
+        <f>L447*M447</f>
+        <v/>
+      </c>
+      <c r="O447" s="5">
+        <f>N447/1000</f>
+        <v/>
+      </c>
+      <c r="P447" s="5" t="inlineStr">
+        <is>
+          <t>10&lt;D&lt;=18mm</t>
+        </is>
+      </c>
+      <c r="Q447" s="5" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ thẩm định tr.70</t>
+        </is>
+      </c>
+      <c r="R447" s="5" t="inlineStr">
+        <is>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="5" t="n">
+        <v>439</v>
+      </c>
+      <c r="B448" s="5" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>Cọc trụ T2 L=30m (tr.70)</t>
+        </is>
+      </c>
+      <c r="D448" s="5" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="E448" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F448" s="5" t="inlineStr">
+        <is>
+          <t>CB400-V</t>
+        </is>
+      </c>
+      <c r="G448" s="5" t="inlineStr"/>
+      <c r="H448" s="5" t="n">
+        <v>2.057</v>
+      </c>
+      <c r="I448" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J448" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K448" s="5">
+        <f>I448*J448</f>
+        <v/>
+      </c>
+      <c r="L448" s="5">
+        <f>H448*K448</f>
+        <v/>
+      </c>
+      <c r="M448" s="5" t="n">
+        <v>2.466</v>
+      </c>
+      <c r="N448" s="5">
+        <f>L448*M448</f>
+        <v/>
+      </c>
+      <c r="O448" s="5">
+        <f>N448/1000</f>
+        <v/>
+      </c>
+      <c r="P448" s="5" t="inlineStr">
+        <is>
           <t>D&gt;18mm</t>
         </is>
       </c>
-      <c r="Q446" s="5" t="inlineStr">
+      <c r="Q448" s="5" t="inlineStr">
         <is>
           <t>Theo bản vẽ thẩm định tr.70</t>
         </is>
       </c>
-      <c r="R446" s="5" t="inlineStr">
-        <is>
-          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.461,59 kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" s="7" t="inlineStr">
+      <c r="R448" s="5" t="inlineStr">
+        <is>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="5" t="n">
+        <v>440</v>
+      </c>
+      <c r="B449" s="5" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t>Cọc trụ T2 L=30m (tr.70)</t>
+        </is>
+      </c>
+      <c r="D449" s="5" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="E449" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F449" s="5" t="inlineStr">
+        <is>
+          <t>CB400-V</t>
+        </is>
+      </c>
+      <c r="G449" s="5" t="inlineStr"/>
+      <c r="H449" s="5" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="I449" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="J449" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K449" s="5">
+        <f>I449*J449</f>
+        <v/>
+      </c>
+      <c r="L449" s="5">
+        <f>H449*K449</f>
+        <v/>
+      </c>
+      <c r="M449" s="5" t="n">
+        <v>2.466</v>
+      </c>
+      <c r="N449" s="5">
+        <f>L449*M449</f>
+        <v/>
+      </c>
+      <c r="O449" s="5">
+        <f>N449/1000</f>
+        <v/>
+      </c>
+      <c r="P449" s="5" t="inlineStr">
+        <is>
+          <t>D&gt;18mm</t>
+        </is>
+      </c>
+      <c r="Q449" s="5" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ thẩm định tr.70</t>
+        </is>
+      </c>
+      <c r="R449" s="5" t="inlineStr">
+        <is>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="5" t="n">
+        <v>441</v>
+      </c>
+      <c r="B450" s="5" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t>Cọc trụ T2 L=30m (tr.70)</t>
+        </is>
+      </c>
+      <c r="D450" s="5" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E450" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F450" s="5" t="inlineStr">
+        <is>
+          <t>CB400-V</t>
+        </is>
+      </c>
+      <c r="G450" s="5" t="inlineStr"/>
+      <c r="H450" s="5" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="I450" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J450" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K450" s="5">
+        <f>I450*J450</f>
+        <v/>
+      </c>
+      <c r="L450" s="5">
+        <f>H450*K450</f>
+        <v/>
+      </c>
+      <c r="M450" s="5" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="N450" s="5">
+        <f>L450*M450</f>
+        <v/>
+      </c>
+      <c r="O450" s="5">
+        <f>N450/1000</f>
+        <v/>
+      </c>
+      <c r="P450" s="5" t="inlineStr">
+        <is>
+          <t>10&lt;D&lt;=18mm</t>
+        </is>
+      </c>
+      <c r="Q450" s="5" t="inlineStr">
+        <is>
+          <t>Theo bản vẽ thẩm định tr.70</t>
+        </is>
+      </c>
+      <c r="R450" s="5" t="inlineStr">
+        <is>
+          <t>Thay theo tr.70 (BBS cũ 108.765,99 kg, bản vẽ 108.884,23 kg) | thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.70 | số thanh trống trên OCR, lấy '4-P11-D16' ở mặt đứng cọc tr.69 — xem PDF tr.70 | khối lượng trống trên OCR, = dài × SL × kg/m = 16.46 — xem PDF tr.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="7" t="inlineStr">
         <is>
           <t>TỔNG CỘNG CỐT THÉP VÀ CÁP DƯL TOÀN BỘ CÔNG TRÌNH</t>
         </is>
       </c>
-      <c r="N447" s="7">
-        <f>SUM(N6:N446)</f>
-        <v/>
-      </c>
-      <c r="O447" s="7">
-        <f>SUM(O6:O446)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="449">
-      <c r="B449" s="7" t="inlineStr">
+      <c r="N451" s="7">
+        <f>SUM(N6:N450)</f>
+        <v/>
+      </c>
+      <c r="O451" s="7">
+        <f>SUM(O6:O450)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" s="7" t="inlineStr">
         <is>
           <t>BẢNG TỔNG HỢP THEO PHÂN NHÓM ĐƯỜNG KÍNH Ø</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="B450" s="7" t="inlineStr">
+    <row r="454">
+      <c r="B454" s="7" t="inlineStr">
         <is>
           <t>Nhóm đường kính</t>
         </is>
       </c>
-      <c r="C450" s="7" t="inlineStr">
+      <c r="C454" s="7" t="inlineStr">
         <is>
           <t>Khối lượng (kg)</t>
         </is>
       </c>
-      <c r="D450" s="7" t="inlineStr">
+      <c r="D454" s="7" t="inlineStr">
         <is>
           <t>Khối lượng (Tấn)</t>
         </is>
       </c>
-      <c r="E450" s="7" t="inlineStr">
+      <c r="E454" s="7" t="inlineStr">
         <is>
           <t>Tỷ trọng (%)</t>
         </is>
       </c>
     </row>
-    <row r="451">
-      <c r="B451" t="inlineStr">
+    <row r="455">
+      <c r="B455" t="inlineStr">
         <is>
           <t>D&lt;=10mm</t>
         </is>
       </c>
-      <c r="C451">
-        <f>SUMIF($P$6:$P$446, "D&lt;=10mm", $N$6:$N$446)</f>
-        <v/>
-      </c>
-      <c r="D451">
-        <f>C451/1000</f>
-        <v/>
-      </c>
-      <c r="E451">
-        <f>C451/$N$447</f>
-        <v/>
-      </c>
-    </row>
-    <row r="452">
-      <c r="B452" t="inlineStr">
+      <c r="C455">
+        <f>SUMIF($P$6:$P$450, "D&lt;=10mm", $N$6:$N$450)</f>
+        <v/>
+      </c>
+      <c r="D455">
+        <f>C455/1000</f>
+        <v/>
+      </c>
+      <c r="E455">
+        <f>C455/$N$451</f>
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="inlineStr">
         <is>
           <t>10&lt;D&lt;=18mm</t>
         </is>
       </c>
-      <c r="C452">
-        <f>SUMIF($P$6:$P$446, "10&lt;D&lt;=18mm", $N$6:$N$446)</f>
-        <v/>
-      </c>
-      <c r="D452">
-        <f>C452/1000</f>
-        <v/>
-      </c>
-      <c r="E452">
-        <f>C452/$N$447</f>
-        <v/>
-      </c>
-    </row>
-    <row r="453">
-      <c r="B453" t="inlineStr">
+      <c r="C456">
+        <f>SUMIF($P$6:$P$450, "10&lt;D&lt;=18mm", $N$6:$N$450)</f>
+        <v/>
+      </c>
+      <c r="D456">
+        <f>C456/1000</f>
+        <v/>
+      </c>
+      <c r="E456">
+        <f>C456/$N$451</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" t="inlineStr">
         <is>
           <t>D&gt;18mm</t>
         </is>
       </c>
-      <c r="C453">
-        <f>SUMIF($P$6:$P$446, "D&gt;18mm", $N$6:$N$446)</f>
-        <v/>
-      </c>
-      <c r="D453">
-        <f>C453/1000</f>
-        <v/>
-      </c>
-      <c r="E453">
-        <f>C453/$N$447</f>
-        <v/>
-      </c>
-    </row>
-    <row r="454">
-      <c r="B454" t="inlineStr">
+      <c r="C457">
+        <f>SUMIF($P$6:$P$450, "D&gt;18mm", $N$6:$N$450)</f>
+        <v/>
+      </c>
+      <c r="D457">
+        <f>C457/1000</f>
+        <v/>
+      </c>
+      <c r="E457">
+        <f>C457/$N$451</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="inlineStr">
         <is>
           <t>Cáp DƯL 15.2mm</t>
         </is>
       </c>
-      <c r="C454">
-        <f>SUMIF($P$6:$P$446, "Cáp DƯL 15.2mm", $N$6:$N$446)</f>
-        <v/>
-      </c>
-      <c r="D454">
-        <f>C454/1000</f>
-        <v/>
-      </c>
-      <c r="E454">
-        <f>C454/$N$447</f>
-        <v/>
-      </c>
-    </row>
-    <row r="455">
-      <c r="B455" s="7" t="inlineStr">
+      <c r="C458">
+        <f>SUMIF($P$6:$P$450, "Cáp DƯL 15.2mm", $N$6:$N$450)</f>
+        <v/>
+      </c>
+      <c r="D458">
+        <f>C458/1000</f>
+        <v/>
+      </c>
+      <c r="E458">
+        <f>C458/$N$451</f>
+        <v/>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="7" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C455">
-        <f>SUM(C451:C454)</f>
-        <v/>
-      </c>
-      <c r="D455">
-        <f>SUM(D451:D454)</f>
+      <c r="C459">
+        <f>SUM(C455:C458)</f>
+        <v/>
+      </c>
+      <c r="D459">
+        <f>SUM(D455:D458)</f>
         <v/>
       </c>
     </row>
@@ -33155,11 +33443,11 @@
         <v>0.222</v>
       </c>
       <c r="E5">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 6, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 6, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F5">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 6, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 6, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G5">
@@ -33187,11 +33475,11 @@
         <v>0.395</v>
       </c>
       <c r="E6">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 8, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 8, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F6">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 8, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 8, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G6">
@@ -33219,11 +33507,11 @@
         <v>0.617</v>
       </c>
       <c r="E7">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 10, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 10, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F7">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 10, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 10, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G7">
@@ -33251,11 +33539,11 @@
         <v>0.888</v>
       </c>
       <c r="E8">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 12, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 12, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F8">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 12, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 12, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G8">
@@ -33283,11 +33571,11 @@
         <v>1.208</v>
       </c>
       <c r="E9">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 14, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 14, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F9">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 14, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 14, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G9">
@@ -33315,11 +33603,11 @@
         <v>1.578</v>
       </c>
       <c r="E10">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 16, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 16, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F10">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 16, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 16, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G10">
@@ -33347,11 +33635,11 @@
         <v>1.998</v>
       </c>
       <c r="E11">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 18, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 18, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F11">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 18, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 18, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G11">
@@ -33379,11 +33667,11 @@
         <v>2.466</v>
       </c>
       <c r="E12">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 20, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 20, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F12">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 20, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 20, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G12">
@@ -33411,11 +33699,11 @@
         <v>2.984</v>
       </c>
       <c r="E13">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 22, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 22, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F13">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 22, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 22, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G13">
@@ -33443,11 +33731,11 @@
         <v>3.853</v>
       </c>
       <c r="E14">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 25, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 25, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F14">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 25, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 25, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G14">
@@ -33475,11 +33763,11 @@
         <v>4.834</v>
       </c>
       <c r="E15">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 28, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 28, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F15">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 28, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 28, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G15">
@@ -33507,11 +33795,11 @@
         <v>6.313</v>
       </c>
       <c r="E16">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 32, THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 32, THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F16">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$446, 32, THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$E$6:$E$450, 32, THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G16">
@@ -33538,11 +33826,11 @@
         </is>
       </c>
       <c r="E17">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$P$6:$P$446, "Cáp DƯL 15.2mm", THONG_KE_THEP_CHI_TIET!$L$6:$L$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$P$6:$P$450, "Cáp DƯL 15.2mm", THONG_KE_THEP_CHI_TIET!$L$6:$L$450)</f>
         <v/>
       </c>
       <c r="F17">
-        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$P$6:$P$446, "Cáp DƯL 15.2mm", THONG_KE_THEP_CHI_TIET!$N$6:$N$446)</f>
+        <f>SUMIF(THONG_KE_THEP_CHI_TIET!$P$6:$P$450, "Cáp DƯL 15.2mm", THONG_KE_THEP_CHI_TIET!$N$6:$N$450)</f>
         <v/>
       </c>
       <c r="G17">
@@ -34137,13 +34425,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>108461.59</v>
+        <v>108884.23</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>108532.96</v>
+        <v>108955.01</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>71.37</v>
+        <v>70.78</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
@@ -34162,7 +34450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -34945,22 +35233,14 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Tổng các trang chi tiết 108.461,59 kg ≠ bảng tổng hợp tr.175 108.884,00 kg (lệch 422,41 kg). Tr.175: D&lt;=10 10,451 t và D&gt;18 97,451 t khớp đúng 3/7/8/8 cọc; nhóm 10&lt;D&lt;=18 ghi 0,982 t nhưng các trang cọc chỉ có 0,559 t — xem PDF tr.175.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>108.461,59 kg</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>108.884,00 kg</t>
-        </is>
-      </c>
+          <t>Số cấu kiện cần xác nhận: Số cọc 3/7/8/8 khớp bảng tổng hợp tr.175 (thép D&lt;=10, D&gt;18 và vữa lấp lòng 14,43 m³ = 3×0,34 + 7×0,59 + 8×0,66 + 8×0,50).</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>tr.175</t>
+          <t>tr.64, tr.66, tr.68, tr.70</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -34978,11 +35258,19 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Số cấu kiện cần xác nhận: Số cọc 3/7/8/8 khớp bảng tổng hợp tr.175 (thép D&lt;=10, D&gt;18 và vữa lấp lòng 14,43 m³ = 3×0,34 + 7×0,59 + 8×0,66 + 8×0,50).</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>THAY THEO BẢN VẼ: BBS cũ 108.765,99 kg; bản vẽ 108.884,23 kg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>108.765,99 kg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>108.884,23 kg</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>tr.64, tr.66, tr.68, tr.70</t>
@@ -34994,33 +35282,27 @@
       <c r="A28" t="n">
         <v>25</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>44</v>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Mố M1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>THAY THEO BẢN VẼ: BBS cũ 108.765,99 kg; bản vẽ 108.461,59 kg</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>108.765,99 kg</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>108.461,59 kg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>tr.64, tr.66, tr.68, tr.70</t>
-        </is>
-      </c>
+          <t>OCR ghi Ø 'DB', Ø8 suy từ kg/m 0.395 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.31</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -35028,21 +35310,21 @@
         <v>26</v>
       </c>
       <c r="B29" t="n">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mố M1</t>
+          <t>Mố M2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>W6(T)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>OCR ghi Ø 'DB', Ø8 suy từ kg/m 0.395 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.31</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -35069,7 +35351,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 51.50 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -35082,7 +35364,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -35091,12 +35373,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>W6(T)</t>
+          <t>W7(T)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -35123,7 +35405,7 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 48.84 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -35136,7 +35418,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -35145,12 +35427,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>W7(T)</t>
+          <t>W9(T)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
+          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -35177,7 +35459,7 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>BẢN VẼ ghi khối lượng 0 dù dài × SL × kg/m = 136.71 kg — sai trên bản vẽ — xem PDF tr.40</t>
+          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -35190,7 +35472,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -35199,12 +35481,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>W9(T)</t>
+          <t>n</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Chủ dự án quyết định 11/10/2026: tính các thanh này (bản vẽ ghi 0 kg là sai sót)</t>
+          <t>OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -35217,7 +35499,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -35226,12 +35508,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '164' và '0' → 1640 mm; số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 4 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -35244,7 +35526,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -35253,12 +35535,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '64' và '0' → 640 mm; kg/m không đọc được, lấy 0.395 như các thanh Ø8 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (12.64); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 50 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -35271,7 +35553,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -35280,12 +35562,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '48' và '0' → 480 mm; khối lượng 1 cấu kiện trống, lấy từ cột tổng (12.32) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -35298,7 +35580,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -35307,12 +35589,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '189' và '0' → 1890 mm; kg/m không đọc được, lấy 1.58 như các thanh Ø16 khác của bảng; khối lượng 1 cấu kiện không đọc được, lấy từ cột tổng (20.90); số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 7 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -35325,21 +35607,21 @@
         <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mố M2</t>
+          <t>Trụ T1, T2 (Bệ móng)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>(?)</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>OCR tách chiều dài thành '159' và '0' → 1590 mm — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.40</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 4) — xem PDF tr.44</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -35352,11 +35634,11 @@
         <v>38</v>
       </c>
       <c r="B41" t="n">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Bệ móng)</t>
+          <t>Trụ T1, T2 (Xà mũ trụ)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -35366,7 +35648,7 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 4) — xem PDF tr.44</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.51</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -35379,7 +35661,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -35393,7 +35675,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.51</t>
+          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.62</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -35406,21 +35688,21 @@
         <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trụ T1, T2 (Xà mũ trụ)</t>
+          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(?)</t>
+          <t>G6a</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT 5) — xem PDF tr.62</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -35433,7 +35715,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -35442,12 +35724,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>G6a</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -35460,7 +35742,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="n">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -35469,12 +35751,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>Thanh neo</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>OCR đọc khối lượng = 217, dài × SL × kg/m = 2.17 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -35487,7 +35769,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -35496,12 +35778,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thanh neo</t>
+          <t>G6a</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc khối lượng = 217, dài × SL × kg/m = 2.17 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.91</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -35514,7 +35796,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -35523,12 +35805,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>G6a</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -35541,7 +35823,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -35550,12 +35832,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>(?)</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.88</t>
+          <t>OCR không đọc được ký hiệu thanh (STT ?) — xem PDF tr.94</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -35568,7 +35850,7 @@
         <v>46</v>
       </c>
       <c r="B49" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -35577,12 +35859,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(?)</t>
+          <t>G6b</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>OCR không đọc được ký hiệu thanh (STT ?) — xem PDF tr.94</t>
+          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.94</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -35595,21 +35877,21 @@
         <v>47</v>
       </c>
       <c r="B50" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dầm chủ Super-T (15 phiến L=38.2m)</t>
+          <t>Dầm ngang (Diaphragm)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>G6b</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>số lượng trống/không đọc được, suy = khối lượng ghi ÷ (dài × kg/m) = 3 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.94</t>
+          <t>hệ số 3 suy từ cột tổng (318.54 ÷ 106.18) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -35622,7 +35904,7 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -35631,12 +35913,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (318.54 ÷ 106.18) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (343.83 ÷ 114.61) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -35649,7 +35931,7 @@
         <v>49</v>
       </c>
       <c r="B52" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -35658,12 +35940,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (343.83 ÷ 114.61) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (737.91 ÷ 245.97) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -35676,7 +35958,7 @@
         <v>50</v>
       </c>
       <c r="B53" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -35685,12 +35967,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (737.91 ÷ 245.97) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (172.92 ÷ 57.64) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -35703,7 +35985,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -35712,12 +35994,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (172.92 ÷ 57.64) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (989.55 ÷ 329.85) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -35730,7 +36012,7 @@
         <v>52</v>
       </c>
       <c r="B55" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -35739,12 +36021,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (989.55 ÷ 329.85) — xem PDF tr.96</t>
+          <t>hệ số 3 suy từ cột tổng (200.37 ÷ 66.79) — xem PDF tr.96</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -35757,21 +36039,21 @@
         <v>53</v>
       </c>
       <c r="B56" t="n">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dầm ngang (Diaphragm)</t>
+          <t>Bản liên tục nhiệt (Link Slab)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>hệ số 3 suy từ cột tổng (200.37 ÷ 66.79) — xem PDF tr.96</t>
+          <t>hệ số 2 suy từ cột tổng (2,837.16 ÷ 1,418.58) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -35798,7 +36080,7 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (2,837.16 ÷ 1,418.58) — xem PDF tr.112</t>
+          <t>OCR ghi Ø 'D1', Ø18 suy từ kg/m 2 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -35811,7 +36093,7 @@
         <v>55</v>
       </c>
       <c r="B58" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -35820,12 +36102,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>OCR ghi Ø 'D1', Ø18 suy từ kg/m 2 — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (5,070.92 ÷ 2,535.46) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -35838,7 +36120,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -35847,12 +36129,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (5,070.92 ÷ 2,535.46) — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (102.66 ÷ 51.33) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -35865,7 +36147,7 @@
         <v>57</v>
       </c>
       <c r="B60" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -35874,12 +36156,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (102.66 ÷ 51.33) — xem PDF tr.112</t>
+          <t>hệ số 2 suy từ cột tổng (907.20 ÷ 453.60) — xem PDF tr.112</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -35892,21 +36174,21 @@
         <v>58</v>
       </c>
       <c r="B61" t="n">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bản liên tục nhiệt (Link Slab)</t>
+          <t>Gờ lan can BTCT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (907.20 ÷ 453.60) — xem PDF tr.112</t>
+          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -35919,7 +36201,7 @@
         <v>59</v>
       </c>
       <c r="B62" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -35928,12 +36210,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (4,016.50 ÷ 211.40) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -35946,7 +36228,7 @@
         <v>60</v>
       </c>
       <c r="B63" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -35955,12 +36237,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (4,016.50 ÷ 211.40) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,209.40 ÷ 116.30) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -35973,7 +36255,7 @@
         <v>61</v>
       </c>
       <c r="B64" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -35982,12 +36264,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>G4A</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,209.40 ÷ 116.30) — xem PDF tr.119</t>
+          <t>khối lượng 1 cấu kiện trống, = dài × SL × kg/m; hệ số 19 = tổng ÷ khối lượng — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -36000,7 +36282,7 @@
         <v>62</v>
       </c>
       <c r="B65" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -36009,12 +36291,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>G4A</t>
+          <t>G4B</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>khối lượng 1 cấu kiện trống, = dài × SL × kg/m; hệ số 19 = tổng ÷ khối lượng — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (85.10 ÷ dài × SL × kg/m 4.48) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -36027,7 +36309,7 @@
         <v>63</v>
       </c>
       <c r="B66" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -36036,12 +36318,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>G4B</t>
+          <t>G4C</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (85.10 ÷ dài × SL × kg/m 4.48) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (139.10 ÷ dài × SL × kg/m 7.32) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -36054,7 +36336,7 @@
         <v>64</v>
       </c>
       <c r="B67" t="n">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -36063,12 +36345,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>G4C</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (139.10 ÷ dài × SL × kg/m 7.32) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -36081,7 +36363,7 @@
         <v>65</v>
       </c>
       <c r="B68" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -36090,12 +36372,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,581.50 ÷ 135.90) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (3,898.30 ÷ 205.20) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -36108,7 +36390,7 @@
         <v>66</v>
       </c>
       <c r="B69" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -36117,12 +36399,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (3,898.30 ÷ 205.20) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (1,292.30 ÷ 68.00) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -36135,7 +36417,7 @@
         <v>67</v>
       </c>
       <c r="B70" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -36144,12 +36426,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>G7</t>
+          <t>G7A</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (1,292.30 ÷ 68.00) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (2,274.30 ÷ 119.70) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -36162,7 +36444,7 @@
         <v>68</v>
       </c>
       <c r="B71" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -36171,12 +36453,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>G7A</t>
+          <t>G8A</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (2,274.30 ÷ 119.70) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (57.00 ÷ 3.00) — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -36189,7 +36471,7 @@
         <v>69</v>
       </c>
       <c r="B72" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -36198,12 +36480,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>G8A</t>
+          <t>G8B</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (57.00 ÷ 3.00) — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (67.10 ÷ dài × SL × kg/m 3.53) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -36216,7 +36498,7 @@
         <v>70</v>
       </c>
       <c r="B73" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -36225,12 +36507,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>G8B</t>
+          <t>G8C</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (67.10 ÷ dài × SL × kg/m 3.53) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>hệ số 19 suy từ cột tổng (91.50 ÷ dài × SL × kg/m 4.81) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -36243,7 +36525,7 @@
         <v>71</v>
       </c>
       <c r="B74" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -36252,12 +36534,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>G8C</t>
+          <t>G8A</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>hệ số 19 suy từ cột tổng (91.50 ÷ dài × SL × kg/m 4.81) — ô số cấu kiện gộp/không đọc được — xem PDF tr.119</t>
+          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -36270,21 +36552,21 @@
         <v>72</v>
       </c>
       <c r="B75" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gờ lan can BTCT</t>
+          <t>Khe co giãn</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>G8A</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>OCR đọc SL = 6, phép tính bản vẽ cho 9 (khối lượng ghi ÷ dài ÷ kg/m) — Σ bảng sau sửa khớp tổng bản vẽ — xem PDF tr.119</t>
+          <t>hệ số 2 suy từ cột tổng (586.67 ÷ 293.33) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -36297,7 +36579,7 @@
         <v>73</v>
       </c>
       <c r="B76" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -36306,12 +36588,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (586.67 ÷ 293.33) — xem PDF tr.121</t>
+          <t>hệ số 2 suy từ cột tổng (521.99 ÷ 260.99) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -36324,7 +36606,7 @@
         <v>74</v>
       </c>
       <c r="B77" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -36333,12 +36615,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (521.99 ÷ 260.99) — xem PDF tr.121</t>
+          <t>hệ số 2 suy từ cột tổng (251.14 ÷ 125.57) — xem PDF tr.121</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -36351,21 +36633,21 @@
         <v>75</v>
       </c>
       <c r="B78" t="n">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Khe co giãn</t>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>hệ số 2 suy từ cột tổng (251.14 ÷ 125.57) — xem PDF tr.121</t>
+          <t>thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.64</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -36373,6 +36655,195 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" t="n">
+        <v>420</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.66</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" t="n">
+        <v>420</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>số thanh trống trên OCR, suy = khối lượng ÷ (dài × kg/m) = 4 — xem PDF tr.66</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" t="n">
+        <v>435</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.68</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" t="n">
+        <v>435</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>số thanh trống trên OCR, suy = khối lượng ÷ (dài × kg/m) = 4 — xem PDF tr.68</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" t="n">
+        <v>450</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>thép treo lồng — bảng phụ, không nằm trong tổng thép chính của trang — xem PDF tr.70</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" t="n">
+        <v>450</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>số thanh trống trên OCR, lấy '4-P11-D16' ở mặt đứng cọc tr.69 — xem PDF tr.70</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" t="n">
+        <v>450</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cọc khoan nhồi D1200 (26 cọc L=872m)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>khối lượng trống trên OCR, = dài × SL × kg/m = 16.46 — xem PDF tr.70</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
